--- a/data/dividends_info_20260811.xlsx
+++ b/data/dividends_info_20260811.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.8650016784668</v>
+        <v>47.75500106811523</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1880288244938862</v>
+        <v>0.1884619369427481</v>
       </c>
       <c r="J2" t="n">
         <v>216</v>
@@ -569,8 +569,12 @@
           <t>IT0001031084</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>67.69999694824219</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.033973458721368</v>
+      </c>
       <c r="J3" t="n">
         <v>195</v>
       </c>
@@ -612,12 +616,8 @@
           <t>IT0005337818</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>9.380000114440918</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.6396588408098992</v>
-      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>125</v>
       </c>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.84000015258789</v>
+        <v>47.75500106811523</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1881270897009633</v>
+        <v>0.1884619369427481</v>
       </c>
       <c r="J6" t="n">
         <v>125</v>
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.150000095367432</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.58139518997746</v>
+        <v>3.598130664738818</v>
       </c>
       <c r="J7" t="n">
         <v>104</v>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.02000045776367</v>
+        <v>24.04999923706055</v>
       </c>
       <c r="I8" t="n">
-        <v>1.124063259177547</v>
+        <v>1.122661158275363</v>
       </c>
       <c r="J8" t="n">
         <v>104</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.59499931335449</v>
+        <v>23.22999954223633</v>
       </c>
       <c r="I9" t="n">
-        <v>2.500529846025751</v>
+        <v>2.53981924936018</v>
       </c>
       <c r="J9" t="n">
         <v>104</v>
@@ -895,10 +895,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.829999923706055</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I10" t="n">
-        <v>3.430531777311974</v>
+        <v>3.424657444766908</v>
       </c>
       <c r="J10" t="n">
         <v>97</v>
@@ -942,10 +942,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.67000007629395</v>
+        <v>10.85000038146973</v>
       </c>
       <c r="I11" t="n">
-        <v>4.311152733934878</v>
+        <v>4.239631187346457</v>
       </c>
       <c r="J11" t="n">
         <v>76</v>
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.599999904632568</v>
+        <v>7.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7894736941171157</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>69</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J13" t="n">
         <v>69</v>
@@ -1130,10 +1130,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.099999904632568</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7450980531486446</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J15" t="n">
         <v>48</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.02000045776367</v>
+        <v>24.04999923706055</v>
       </c>
       <c r="I16" t="n">
-        <v>1.124063259177547</v>
+        <v>1.122661158275363</v>
       </c>
       <c r="J16" t="n">
         <v>41</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.995000004768372</v>
+        <v>1.996000051498413</v>
       </c>
       <c r="I17" t="n">
-        <v>2.857142850313825</v>
+        <v>2.855711349166031</v>
       </c>
       <c r="J17" t="n">
         <v>41</v>
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>47.84000015258789</v>
+        <v>47.75500106811523</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1881270897009633</v>
+        <v>0.1884619369427481</v>
       </c>
       <c r="J18" t="n">
         <v>41</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>98.30000305175781</v>
+        <v>97.34999847412109</v>
       </c>
       <c r="I19" t="n">
-        <v>1.353000975289611</v>
+        <v>1.366204438465974</v>
       </c>
       <c r="J19" t="n">
         <v>41</v>
@@ -1365,10 +1365,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.800000190734863</v>
+        <v>5.699999809265137</v>
       </c>
       <c r="I20" t="n">
-        <v>5.172413623006964</v>
+        <v>5.263158070853988</v>
       </c>
       <c r="J20" t="n">
         <v>34</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J21" t="n">
         <v>13</v>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.759999990463257</v>
+        <v>2.779999971389771</v>
       </c>
       <c r="I22" t="n">
-        <v>7.971014520296202</v>
+        <v>7.913669146191328</v>
       </c>
       <c r="J22" t="n">
         <v>-1</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.099999904632568</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7450980531486446</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J23" t="n">
         <v>-8</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.599999904632568</v>
+        <v>2.619999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>5.69111559336426</v>
+        <v>5.647672002414033</v>
       </c>
       <c r="J25" t="n">
         <v>-8</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.960000038146973</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I26" t="n">
-        <v>4.194630845635492</v>
+        <v>4.173622863984384</v>
       </c>
       <c r="J26" t="n">
         <v>-15</v>
@@ -1694,10 +1694,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.190000057220459</v>
+        <v>4.199999809265137</v>
       </c>
       <c r="I27" t="n">
-        <v>3.34128873718614</v>
+        <v>3.333333484710216</v>
       </c>
       <c r="J27" t="n">
         <v>-22</v>
@@ -1741,10 +1741,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.923000335693359</v>
+        <v>9.847000122070312</v>
       </c>
       <c r="I28" t="n">
-        <v>2.620175261556441</v>
+        <v>2.640398058056848</v>
       </c>
       <c r="J28" t="n">
         <v>-22</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.80000019073486</v>
+        <v>13.84000015258789</v>
       </c>
       <c r="I29" t="n">
-        <v>4.347826026863623</v>
+        <v>4.335260067810101</v>
       </c>
       <c r="J29" t="n">
         <v>-22</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.680000066757202</v>
+        <v>2.661999940872192</v>
       </c>
       <c r="I30" t="n">
-        <v>8.20895501940042</v>
+        <v>8.264462993485942</v>
       </c>
       <c r="J30" t="n">
         <v>-22</v>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.492000013589859</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8130081076246635</v>
       </c>
       <c r="J31" t="n">
         <v>-22</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.440000057220459</v>
+        <v>6.425000190734863</v>
       </c>
       <c r="I32" t="n">
-        <v>1.552795017259062</v>
+        <v>1.556420187258585</v>
       </c>
       <c r="J32" t="n">
         <v>-22</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>18.95000076293945</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="I33" t="n">
-        <v>1.984168785551417</v>
+        <v>2.04347830323506</v>
       </c>
       <c r="J33" t="n">
         <v>-22</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.650000095367432</v>
+        <v>5.670000076293945</v>
       </c>
       <c r="I35" t="n">
-        <v>2.123893769460125</v>
+        <v>2.116402087924397</v>
       </c>
       <c r="J35" t="n">
         <v>-29</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5747126562779011</v>
       </c>
       <c r="J36" t="n">
         <v>-29</v>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.839999914169312</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="I37" t="n">
-        <v>5.281690300468702</v>
+        <v>5.136986167150362</v>
       </c>
       <c r="J37" t="n">
         <v>-29</v>
@@ -3064,333 +3064,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Altea Green Power S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Avio S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>BolognaFiere S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>EPH INVEST S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EQUITA GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FNM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>IMMSI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Orsero S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SOL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SYS-DAT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Toscana Aeroporti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>UNIDATA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>